--- a/01_경혈별_해부생리_분석보고서/PC_수궐음심포경/PC09_중충/PC09_중충_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/PC_수궐음심포경/PC09_중충/PC09_중충_해부생리_분석데이터.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +503,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,6 +866,101 @@
       </c>
       <c r="F5" t="n">
         <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>("PC9" OR "Zhongchong" OR "中冲") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy) | ("PC9" OR "Zhongchong" OR "中冲") AND ("Zhongguo Zhen Jiu"[Journal] OR "Zhen Ci Yan Jiu"[Journal])</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:52</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>doi_starts_with:10.13703,title_and_abstract.search:"Zhongchong" OR "PC9" | doi_starts_with:10.13702,title_and_abstract.search:"Zhongchong" OR "PC9" | has_doi:true,title_and_abstract.search:"Zhongchong" OR "PC9" AND (acupuncture OR electroacupuncture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:52</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Zhongchong acupuncture nerve reflex</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:52</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>26</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>merged_into_existing=18 batch_dups=8 sources={'pubmed': 'ok', 'openalex': 'ok', 'crossref': 'ok'}</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -879,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1187,6 +1282,472 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>작성자 지침</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가, 횡단면 모식도·FMA 경로도 추가. ARI·B-Check 불변</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>fma_query.py profile PC09; 보고서 4·6·8절·부록 A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>교재 용어</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FMA_ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FMA_label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>대응 수준</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>출처 교재</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>지배신경(FMA nerve_supply)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>상위 줄기(FMA)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>척수 분절(FMA segmental_supply)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>깊은손가락굽힘근 (flexor digitorum profundus)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>38478</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Flexor digitorum profundus</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FMA:44831 Nerve to flexor digitorum profundus; FMA:65351 Branch of ulnar nerve to flexor digitorum profundus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Anterior interosseous nerve → Peripheral segment of median nerve</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>C8(primary/segmental), T1(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>FMA contained_in 위팔 앞칸 = 모델링 오류. 자침 경로 밖(기저부 부착)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>정중신경의 고유바닥쪽손가락가지 (proper palmar digital branch of the median nerve)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>44853</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Proper palmar digital branch of median nerve</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FMA:14385 Median nerve</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>등쪽손가락신경 (dorsal digital nerve)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>75490</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Set of dorsal digital branches of radial nerve</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>용어 일치·위치 불일치 — 노신경 집합. 가운데손가락 끝마디 등쪽은 정중신경 등쪽가지(B1-03). 근거로 쓰지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>고유바닥쪽손가락신경 (proper palmar digital nerve)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>75484</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Set of proper palmar digital nerves</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>집합 실체</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>등쪽손가락동ㆍ정맥 (dorsal digital artery and vein); 등쪽손가락동맥 (dorsal digital artery)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>321492</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Dorsal digital artery</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FMA:22730 Radial artery → FMA:3951 Subclavian artery</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>등쪽손가락동ㆍ정맥 (dorsal digital artery and vein)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>70917</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Set of dorsal digital veins</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>집합 실체</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>바닥쪽손가락정맥 (palmar digital vein)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>70895</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Set of palmar digital veins</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>집합 실체</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>고유바닥쪽손가락동맥 (proper palmar digital artery)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>70804</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Set of proper palmar digital arteries</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>집합 실체</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>분절 합집합</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>C8, T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>교재 비교</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>공통 4 · 공통교재 단독 2 · 김재효 단독 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 로컬 색인, fma_query.py profile PC09 (2026-10-23). B1 보조(등록부 미등재)</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1788,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1487,7 +2047,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1745,7 +2304,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1919,7 +2477,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -2115,7 +2672,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>

--- a/01_경혈별_해부생리_분석보고서/PC_수궐음심포경/PC09_중충/PC09_중충_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/PC_수궐음심포경/PC09_중충/PC09_중충_해부생리_분석데이터.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_분기추론_TriTarget" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -974,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1304,6 +1305,116 @@
       <c r="D15" t="inlineStr">
         <is>
           <t>fma_query.py profile PC09; 보고서 4·6·8절·부록 A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-25 2.7.7 · 1절</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3대 원전</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4대 원전, 《经络通鉴》 7행(+색인) — 시트 문헌고증_DB 하단 블록</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>정본 1절·Rank 1 &amp; 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-25 2.7.7 · 1·9절 证治</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>요지 '구토'</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한글번역 '딸꾹질과 구토가 끝없는 것(哕呕无度)'으로 수정(哕 누락 차이 기록), 9절 한글번역 포인터</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>정본 Rank 1 &amp; 2; 中国针灸证治通鉴_08_第壹编_第七篇_足少阴肾经_手厥阴心包经_手少阳三焦经_한글번역.md L664~684</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-25 2.7.7 · 4·7절</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>단일 Target, 변이 Δ 10~15mm &lt; 15mm</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tri-Target 3행·쌍별 Δ(0~3mm, 모두 병합) → Target 1≡2≡3; 변이는 10mm 초과 가능하나 정의 밖 → 분기 대상 아님; 시트 7_분기추론_TriTarget 신설</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>정본 Rank 5 Tri-Target(Δ &gt; 10mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-25 2.7.7 · 10절</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>④ 通考 교감</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>④ 通考·经络通鉴 교감 재검 — 점수 불변(67.5 ± 1.2 C, SI 100)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>정본 Rank 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ARI_v3.0 (2026-10-25 재채점)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>④ A 50 / B 50, ARI-Core 67.5 ± 1.2 (C), 민감도 65.6 (C)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>④ A 75 / B 75, S_orig 75 / 81.25, ARI-Core 70.0 ± 1.2 (B), 민감도 67.7 (C, 가중치 민감). 변이 정위는 Target 제외 규칙 적용</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 22편 L604·L621, 07편 L300, 27편 L641, 26편 L204~219; 정본 4.2·Rank 5·Rank 7</t>
         </is>
       </c>
     </row>
@@ -1756,13 +1867,353 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>7. 공간 변위 분기 추론도 (Tri-Target, 분기 기준 Δ &gt; 10mm) — 좌표는 일반 말절 크기 추정, 실측 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>정의·근거</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>포인터</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Target 1 고전 문헌 위치</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>《灵枢·本输》 "手中指之端"</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0 (지첨)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0~2.3mm</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>通考(下)_81-160 L1642; 中国针灸经络通鉴_26_第叁编_第九篇_手厥阴经脉、经别、络脉和经筋.md L235</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Target 2 촉진 실체화 위치</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>《明堂经》 "去爪甲如韭叶陷者中"</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>약 0~+3mm(손톱 유리연에서 부추잎 너비 ≈1푼, 추정)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0~2.3mm</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>通考 L1643; 《针灸学简编》 "去指甲游离缘约一分处". 자입 기준점: 간극 불명확(지첨에 근육·힘줄 없음), 기준 구조 손톱 FMA:54335</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Target 3 현대 WHO 위치</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WHO 2008 "centre of the tip of the middle finger"</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0~2.3mm</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>WHO 2008; 4~7판 교재</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>(Target 아님) 변이 정위</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>《窦太师针经》·《徐氏针灸大全》 이후 요측 손톱뿌리각 상방 0.1촌</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>약 −5~−7mm</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>약 +10~+13mm</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0~2.3mm</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>通考 L1654 — Tri-Target 정의 밖 후대 이설</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>쌍별 편차표 (모두 추정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>쌍</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Δ (추정)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Target 1 – Target 2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>약 0~3mm</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>같은 지첨; 차이는 부추잎 너비(≈1푼)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>≤ 10mm → 병합</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Target 1 – Target 3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>약 0mm</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>둘 다 중지 끝 중앙</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>≤ 10mm → 병합</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Target 2 – Target 3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>약 0~3mm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>《针灸学简编》도 같은 점으로 기술</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>≤ 10mm → 병합</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>단일 Target 1≡2≡3 (분기 없음)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>구판 이중 채점 승계, 점수 불변</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>변이 정위</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>첨단 중앙과 약 10~15mm</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>새 기준 10mm 초과 가능하나 Tri-Target 정의 밖 → 분기 대상 아님</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>채점자 A 예비 점수 S_orig 50/S_clarity 50/S_reflex 50/SI 100 → ARI-Core 50.0 (D) — 단일 채점(예비), 이중 채점 필요, 판정 미사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>구판 대응</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>구 단일 Target('첨단 중앙, 고전·WHO 공통') → Target 1≡2≡3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>구판 채점자 A 'T2'(변이) → Target 번호 없음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2007,6 +2458,346 @@
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>고전 원전 정위와 100% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-25 추가 — 《中国针灸经络通鉴》 교감 (4대 원전, Framework 2.7.7). 이 블록은 v2.7.7 정본(.md 1절)과 같은 내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>문헌</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>원문 발췌</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>한국어 요지</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>내부 포인터(파일·행)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Tri-Target 관련</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>《经络通鉴》 경맥</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>《灵枢·经脉》 "入掌中，循中指出其端" / 注 "中冲穴也"·"中指端，中冲也，手厥阴经止于此"</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>경맥 순행 끝 = 중충</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_26_第叁编_第九篇_手厥阴经脉、经别、络脉和经筋.md L84·129·154·180</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Target 1 일치</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>새 위치 정보 없음</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>《经络通鉴》 邪客</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>《灵枢·邪客》 "心主之脉，出于中指之端，内屈循中指内廉" / 马莳·张介宾 注</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>中指之端 = 중충, 内廉 = 순행로</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_26_第叁编_第九篇_手厥阴经脉、经别、络脉和经筋.md L204·208·219</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>변이(요측 손톱각) 원인 맥락</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>경락론적 확장(Rank 4)</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>《经络通鉴》 本输</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>"心出于中冲" / 张介宾 "心与心胞，本同一藏" / 张志聪 "中冲，包络之经也" / 马莳 "不言心经者"</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>심/심포 귀속 주석사</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_26_第叁编_第九篇_手厥阴经脉、经别、络脉和经筋.md L235·262·266; 中国针灸经络通鉴_22_第叁编_第五篇_手少阴经脉、经别、络脉和经筋.md L295</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>3절 보강</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>《经络通鉴》 缪刺(尸厥)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>《甲乙》 "（《素问》又云后刺手心主者，非也。）" / 新校正 / 【按】 "手心主…当删"</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>'手心主'(王冰=中冲) 연문</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_22_第叁编_第五篇_手少阴经脉、经别、络脉和经筋.md L604·621; 中国针灸经络通鉴_07_第壹编_第五篇_不同来源的经络学说.md L300</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Rank 4 전사 오류; 보고서 미사용 조문</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>④ 재채점: 50 → 75 근거(2026-10-25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>《经络通鉴》 缪刺(手少阳)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>张志聪 "当刺中指心包络之中冲，次指手少阳之关冲" / 【按】 "张氏误解…欠妥"</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>中指次指 오독</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_27_第叁编_第十篇_手少阳经脉、经别、络脉和经筋.md L639·641</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Rank 4 주석 오독 배제</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>④ 재채점: 50 → 75 근거(2026-10-25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>《经络通鉴》 缪刺(耳聋)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>马莳 "刺中指爪甲上与肉交者，即中冲穴也"</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>이롱 조문의 중충 특정은 주석</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_18_第叁编_第二篇_手阳明经脉、经别、络脉和经筋.md L800</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>9절 이롱 행 보강</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>《经络通鉴》 脉名索引</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>◇手心主·◇手厥阴·◇手心主之筋 등</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>쪽 번호 색인만</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_37_第伍编_附篇一_脉名索引.md L213~231·337~357</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>검색 범위 기록</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>《证治通鉴》 한글번역</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>《素问》 主耳聋 / 《圣惠方》 小儿夜啼 / 《素问保命集》 哕呕无度</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>한글번역: '딸꾹질과 구토가 끝없는 것' — 구판 요지 '구토'는 哕 누락</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴_08_第壹编_第七篇_足少阴肾经_手厥阴心包经_手少阳三焦经_한글번역.md L664~684</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>1절 한국어 기술 수정</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>9절 포인터: 14편 L1400, 15편 L318·1291·1395, 17편 L158, 22편 L2237, 23편 L1008, 24편 L1461(각 편 _한글번역.md)</t>
         </is>
       </c>
     </row>
@@ -2834,7 +3625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2877,7 +3668,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T1 첨단 중앙(단일)</t>
+          <t>T1≡2≡3 첨단 중앙(단일)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2885,14 +3676,20 @@
           <t>S_orig</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="D2" t="n">
-        <v>75</v>
-      </c>
-      <c r="E2" t="n">
-        <v>71.875</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>81.25</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>78.125</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2908,7 +3705,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T1 첨단 중앙(단일)</t>
+          <t>T1≡2≡3 첨단 중앙(단일)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2939,7 +3736,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T1 첨단 중앙(단일)</t>
+          <t>T1≡2≡3 첨단 중앙(단일)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2970,7 +3767,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T1 첨단 중앙(단일)</t>
+          <t>T1≡2≡3 첨단 중앙(단일)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3001,7 +3798,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡2≡3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3022,7 +3819,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡2≡3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3043,7 +3840,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡2≡3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3064,22 +3861,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡2≡3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S_orig ④ 通考 교감 전사 오류 교정</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="n">
-        <v>50</v>
-      </c>
-      <c r="E9" t="n">
-        <v>50</v>
+          <t>S_orig ④ 通考·经络通鉴 교감 전사 오류 교정</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -3100,8 +3903,10 @@
           <t>ARI-Core A</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>66.25</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>68.75</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -3110,8 +3915,10 @@
           <t>ARI-Core B</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>68.75</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>71.25</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -3120,8 +3927,10 @@
           <t>ARI-Core 평균</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>67.5</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -3130,8 +3939,10 @@
           <t>반범위(±)</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1.2</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -3142,7 +3953,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C (가능·가설)</t>
+          <t>B (개연) — 평균이 B 하한(70), 채점자 A 68.75는 C: 경계 근접</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3965,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>없음(H·⚠ 해당 없음)</t>
+          <t>가중치 민감 (H·⚠ 해당 없음)</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3999,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>65.6 (C, 등급 불변)</t>
+          <t>67.7 (C, 등급 변동 → 가중치 민감)</t>
         </is>
       </c>
     </row>
@@ -3224,7 +4035,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>채점자 A만 요측 손톱뿌리각 변이(窦太师 이후)를 T2로 분리했으나 첨단 중앙과의 거리는 약 10~15mm로 정본 Rank 5 분기 기준(Δ&gt;15mm) 미충족 → 단일 Target으로 조정, 변이는 본문 정위 절에 주석으로 기술(참고: A의 T2 점수 S_orig 50 / S_clarity 50 / S_reflex 50 / SI 100). conflicts 기록은 직접 상충이 아님.</t>
+          <t>채점자 A만 요측 손톱뿌리각 변이(窦太师 이후)를 T2로 분리했으나 첨단 중앙과의 거리는 약 10~15mm로 정본 Rank 5 분기 기준(Δ&gt;15mm) 미충족 → 단일 Target으로 조정, 변이는 본문 정위 절에 주석으로 기술(참고: A의 T2 점수 S_orig 50 / S_clarity 50 / S_reflex 50 / SI 100). conflicts 기록은 직접 상충이 아님. / 2026-10-25 재검: 분기 기준 Δ&gt;10mm로 하향되었으나 변이는 Tri-Target 정의 밖 후대 이설 → 분기 대상 아님. 점수 불변.</t>
         </is>
       </c>
     </row>
@@ -3236,7 +4047,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARI v3.0 | ARI-Core 67.5 ± 1.2 (C) | SI 100 | 잠정 가중치 0.40/0.35/0.25 | 민감도(등가중치): 65.6 (C, 등급 불변)</t>
+          <t>ARI v3.0 | ARI-Core 70.0 ± 1.2 (B) | SI 100 | 잠정 가중치 0.40/0.35/0.25 | 민감도(등가중치): 67.7 (C, 가중치 민감)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Framework 2.7.7 재검</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>점수 불변 — 구 단일 Target → Target 1≡2≡3(세 위치 Δ ≤ 10mm). ④ 《经络通鉴》 재검(《素问·缪刺论》 手心主 연문, 张志聪 오독) — 보고서 미사용 주치 조문이라 단계 불변(50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-25 재채점</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>④ 50 → 75(두 채점자 공통): 《经络通鉴》의 《素问·缪刺论》 '后刺手心主' 연문(22편 L604·L621, 07편 L300), 张志聪 '中冲·关冲' 오독(27편 L641), 《邪客》 '中指之端'(혈)/'内廉'(순행로) 구분(26편 L204~219)을 '경미한 전사 이문 교정' 단계로 반영. S_orig A 75 / B 81.25, ARI-Core 67.5 ± 1.2 (C) → 70.0 ± 1.2 (B, 가중치 민감). 요측 손톱각 변이는 정본 Rank 5 Target 제외 규칙으로 채점 대상 아님</t>
         </is>
       </c>
     </row>
